--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6763-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6763-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95DFCBB6-555A-4D9E-A04F-493838E5A08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5509D1E-6956-4106-8FDF-ED01BB642581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{060BBD2E-A8F9-417E-81FC-E233433C765B}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{44D2914F-F4E7-4DF3-8D16-D7F39AE7C014}"/>
   </bookViews>
   <sheets>
     <sheet name="6763-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1576,25 +1576,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8804B010-27E6-455B-9DA3-8AC186521042}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75A0B60-3ADF-4065-855E-FD84EB66AFC4}">
   <dimension ref="A1:R25"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" customWidth="1"/>
-    <col min="7" max="9" width="7.44140625" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="13" width="7.44140625" customWidth="1"/>
-    <col min="14" max="14" width="7.77734375" customWidth="1"/>
-    <col min="15" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1748,7 +1748,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1828,7 +1828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51">
         <v>2025</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="53">
         <v>2024</v>
       </c>
@@ -2104,7 +2104,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="51">
         <v>2023</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>3.21</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2326,7 +2326,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="53">
         <v>2022</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
         <v>2021</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>2.65</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2602,7 +2602,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="55" t="s">
         <v>27</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="56"/>
       <c r="B22" s="24" t="s">
         <v>46</v>
@@ -2680,7 +2680,7 @@
       <c r="Q22" s="60"/>
       <c r="R22" s="60"/>
     </row>
-    <row r="23" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>27</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>1.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="53">
         <v>2020</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="51" t="s">
         <v>50</v>
       </c>
